--- a/exports/AUROPHARMA_full_report.xlsx
+++ b/exports/AUROPHARMA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.63</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44574.55208333334</v>
+        <v>44575.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>718.95</v>
+        <v>689.6</v>
       </c>
       <c r="I2" t="n">
         <v>701.0577999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.82</v>
+        <v>-4.87</v>
       </c>
       <c r="L2" t="n">
-        <v>1.86</v>
+        <v>5.58</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>4.58</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>3.19</v>
       </c>
       <c r="O2" t="n">
         <v>3.56</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.28</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>649.2</v>
+        <v>658.5</v>
       </c>
       <c r="I3" t="n">
         <v>656.7904793875749</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>5.86</v>
+        <v>4.51</v>
       </c>
       <c r="L3" t="n">
         <v>2.23</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44610.55208333334</v>
+        <v>44613.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>655.8</v>
+        <v>650</v>
       </c>
       <c r="I4" t="n">
         <v>652.6217605113102</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.41</v>
+        <v>-1.29</v>
       </c>
       <c r="L4" t="n">
-        <v>2.34</v>
+        <v>2.76</v>
       </c>
       <c r="M4" t="n">
         <v>1.29</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.82</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44630.55208333334</v>
+        <v>44631.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>629.4</v>
+        <v>643.6</v>
       </c>
       <c r="I5" t="n">
         <v>642.3214624087054</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>3.17</v>
+        <v>0.98</v>
       </c>
       <c r="L5" t="n">
         <v>1.07</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44650.55208333334</v>
+        <v>44651.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>675.1</v>
+        <v>671.65</v>
       </c>
       <c r="I6" t="n">
         <v>672.7858931200874</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>4.89</v>
+        <v>4.36</v>
       </c>
       <c r="L6" t="n">
         <v>4.06</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>542.5</v>
+        <v>546.8</v>
       </c>
       <c r="I7" t="n">
         <v>543.545645535138</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>97.16666666666667</v>
+        <v>98</v>
       </c>
       <c r="K7" t="n">
-        <v>19.23</v>
+        <v>18.59</v>
       </c>
       <c r="L7" t="n">
         <v>6.41</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>5.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>541.85</v>
+        <v>530</v>
       </c>
       <c r="I8" t="n">
         <v>532.0656777516999</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.91</v>
+        <v>-3.07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
         <v>0.83</v>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
         <v>0.84</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>546.5</v>
+        <v>554.95</v>
       </c>
       <c r="I9" t="n">
         <v>554.5082149199667</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.11</v>
+        <v>-4.71</v>
       </c>
       <c r="L9" t="n">
-        <v>4.15</v>
+        <v>5.18</v>
       </c>
       <c r="M9" t="n">
         <v>0.66</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.36</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>567.55</v>
+        <v>555.7</v>
       </c>
       <c r="I10" t="n">
         <v>556.302196963429</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>2.27</v>
+        <v>0.14</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -1011,7 +1130,7 @@
         <v>0.38</v>
       </c>
       <c r="N10" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="O10" t="n">
         <v>2.27</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.37</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44834.55208333334</v>
+        <v>44837.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>509.8</v>
+        <v>535</v>
       </c>
       <c r="I11" t="n">
         <v>526.9895987117723</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>8.26</v>
+        <v>3.73</v>
       </c>
       <c r="L11" t="n">
         <v>2.47</v>
@@ -1068,7 +1199,7 @@
         <v>1.47</v>
       </c>
       <c r="N11" t="n">
-        <v>2.79</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>-2.84</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.01</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44844.55208333334</v>
+        <v>44845.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>535.5</v>
+        <v>516.25</v>
       </c>
       <c r="I12" t="n">
         <v>519.8575842698215</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09</v>
+        <v>-3.5</v>
       </c>
       <c r="L12" t="n">
         <v>4.71</v>
@@ -1125,7 +1268,7 @@
         <v>0.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.79</v>
+        <v>4.94</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.2</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>537.1</v>
+        <v>547.5</v>
       </c>
       <c r="I13" t="n">
         <v>538.7703627220301</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.04</v>
+        <v>-6.05</v>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>6.88</v>
       </c>
       <c r="M13" t="n">
         <v>1.56</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.56</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>541.5</v>
+        <v>484.45</v>
       </c>
       <c r="I14" t="n">
         <v>530.7814806784872</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1</v>
+        <v>-11.52</v>
       </c>
       <c r="L14" t="n">
-        <v>1.93</v>
+        <v>11.74</v>
       </c>
       <c r="M14" t="n">
-        <v>0.13</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>11.57</v>
       </c>
       <c r="O14" t="n">
         <v>2.37</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.4</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>438.2</v>
+        <v>455.4</v>
       </c>
       <c r="I15" t="n">
         <v>453.9591291554482</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>9.550000000000001</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>11.3</v>
@@ -1296,7 +1475,7 @@
         <v>1.28</v>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>3.79</v>
       </c>
       <c r="O15" t="n">
         <v>-11.57</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>437</v>
+        <v>418.9</v>
       </c>
       <c r="I16" t="n">
         <v>432.4863178611104</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.04</v>
+        <v>-8.01</v>
       </c>
       <c r="L16" t="n">
-        <v>5.75</v>
+        <v>8.51</v>
       </c>
       <c r="M16" t="n">
         <v>0.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>4.43</v>
       </c>
       <c r="O16" t="n">
         <v>3.79</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.22</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>421</v>
+        <v>433.5</v>
       </c>
       <c r="I17" t="n">
         <v>425.8204521316096</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5</v>
+        <v>-3.49</v>
       </c>
       <c r="L17" t="n">
         <v>4.62</v>
@@ -1410,7 +1613,7 @@
         <v>0.29</v>
       </c>
       <c r="N17" t="n">
-        <v>2.79</v>
+        <v>5.94</v>
       </c>
       <c r="O17" t="n">
         <v>-4.43</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.25</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>457.75</v>
+        <v>454</v>
       </c>
       <c r="I18" t="n">
         <v>454.1355448435826</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>5.59</v>
+        <v>4.73</v>
       </c>
       <c r="L18" t="n">
         <v>4.15</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>4.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>458</v>
+        <v>474.2</v>
       </c>
       <c r="I19" t="n">
         <v>469.5554928748703</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.88</v>
+        <v>-4.45</v>
       </c>
       <c r="L19" t="n">
-        <v>3.63</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>0.38</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>3.93</v>
       </c>
       <c r="O19" t="n">
         <v>-0.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.8</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>610.75</v>
+        <v>597.45</v>
       </c>
       <c r="I20" t="n">
         <v>607.9162121099102</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>28.8</v>
+        <v>25.99</v>
       </c>
       <c r="L20" t="n">
         <v>3.42</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45075.55208333334</v>
+        <v>45076.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>610.75</v>
+        <v>643</v>
       </c>
       <c r="I21" t="n">
         <v>626.8345147200972</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.23</v>
+        <v>-7.62</v>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>6.34</v>
       </c>
       <c r="O21" t="n">
         <v>-3.44</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>829</v>
+        <v>825.85</v>
       </c>
       <c r="I22" t="n">
         <v>828.1775444269989</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>87</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>28.93</v>
+        <v>28.44</v>
       </c>
       <c r="L22" t="n">
         <v>4.67</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>834</v>
+        <v>858.65</v>
       </c>
       <c r="I23" t="n">
         <v>853.9608289015521</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.99</v>
+        <v>-3.97</v>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>3.98</v>
       </c>
       <c r="M23" t="n">
         <v>0.57</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.34</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>885.75</v>
+        <v>872.2</v>
       </c>
       <c r="I24" t="n">
         <v>877.7445987455633</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>3.16</v>
+        <v>1.58</v>
       </c>
       <c r="L24" t="n">
         <v>3.12</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.91</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45236.55208333334</v>
+        <v>45237.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>878</v>
+        <v>897.65</v>
       </c>
       <c r="I25" t="n">
         <v>890.6423568241398</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.66</v>
+        <v>-2.92</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>3.65</v>
       </c>
       <c r="M25" t="n">
         <v>0.86</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
         <v>-2.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.21</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1152.75</v>
+        <v>1070.65</v>
       </c>
       <c r="I26" t="n">
         <v>1089.483015082194</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>85.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>28.42</v>
+        <v>19.27</v>
       </c>
       <c r="L26" t="n">
         <v>2.94</v>
@@ -1923,7 +2234,7 @@
         <v>0.68</v>
       </c>
       <c r="N26" t="n">
-        <v>2.77</v>
+        <v>7.14</v>
       </c>
       <c r="O26" t="n">
         <v>2.68</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>12.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1024.05</v>
+        <v>1101.5</v>
       </c>
       <c r="I27" t="n">
         <v>1077.835739723628</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>4.35</v>
+        <v>-2.88</v>
       </c>
       <c r="L27" t="n">
         <v>7.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>5.46</v>
       </c>
       <c r="N27" t="n">
-        <v>1.88</v>
+        <v>6.25</v>
       </c>
       <c r="O27" t="n">
         <v>-7.14</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.8</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1028.8</v>
+        <v>1003.6</v>
       </c>
       <c r="I28" t="n">
         <v>1019.234550823861</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.6</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>7.2</v>
+        <v>10.57</v>
       </c>
       <c r="M28" t="n">
         <v>0.18</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45378.38541666666</v>
+        <v>45378.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1065.05</v>
+        <v>1070</v>
       </c>
       <c r="I29" t="n">
         <v>1069.219123582965</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.12</v>
+        <v>-6.62</v>
       </c>
       <c r="L29" t="n">
-        <v>6.62</v>
+        <v>7.1</v>
       </c>
       <c r="M29" t="n">
         <v>1.43</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.83</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1164</v>
+        <v>1100.55</v>
       </c>
       <c r="I30" t="n">
         <v>1111.246535083672</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>8.789999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="L30" t="n">
         <v>0.5600000000000001</v>
@@ -2151,7 +2510,7 @@
         <v>1.67</v>
       </c>
       <c r="N30" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>1.79</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1171</v>
+        <v>1201.3</v>
       </c>
       <c r="I31" t="n">
         <v>1186.958306582225</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.4</v>
+        <v>-9.15</v>
       </c>
       <c r="L31" t="n">
-        <v>8.15</v>
+        <v>10.13</v>
       </c>
       <c r="M31" t="n">
         <v>0.52</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.72</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1527.95</v>
+        <v>1495.5</v>
       </c>
       <c r="I32" t="n">
         <v>1501.210714276568</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>124.1666666666667</v>
+        <v>125</v>
       </c>
       <c r="K32" t="n">
-        <v>27.19</v>
+        <v>24.49</v>
       </c>
       <c r="L32" t="n">
         <v>7.65</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.04</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1248</v>
+        <v>1266.7</v>
       </c>
       <c r="I33" t="n">
         <v>1254.328914169144</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K33" t="n">
-        <v>16.55</v>
+        <v>15.3</v>
       </c>
       <c r="L33" t="n">
         <v>3.03</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.8</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1301.85</v>
+        <v>1264.7</v>
       </c>
       <c r="I34" t="n">
         <v>1283.964893488249</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>2.77</v>
+        <v>-0.16</v>
       </c>
       <c r="L34" t="n">
         <v>2.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.04</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1193.9</v>
+        <v>1253.55</v>
       </c>
       <c r="I35" t="n">
         <v>1223.082621992559</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>5.6</v>
+        <v>0.88</v>
       </c>
       <c r="L35" t="n">
         <v>3.34</v>
       </c>
       <c r="M35" t="n">
-        <v>0.48</v>
+        <v>1.77</v>
       </c>
       <c r="N35" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>-1.94</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1212</v>
+        <v>1170.3</v>
       </c>
       <c r="I36" t="n">
         <v>1174.1700216503</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.31</v>
+        <v>-6.64</v>
       </c>
       <c r="L36" t="n">
-        <v>4.48</v>
+        <v>7.52</v>
       </c>
       <c r="M36" t="n">
-        <v>0.14</v>
+        <v>0.99</v>
       </c>
       <c r="N36" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
         <v>4</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.92</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1172.5</v>
+        <v>1198.35</v>
       </c>
       <c r="I37" t="n">
         <v>1197.332831045948</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.19</v>
+        <v>-2.4</v>
       </c>
       <c r="L37" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="M37" t="n">
         <v>0.77</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.91</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1138.55</v>
+        <v>1108.05</v>
       </c>
       <c r="I38" t="n">
         <v>1122.052986095679</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.99</v>
+        <v>-7.54</v>
       </c>
       <c r="L38" t="n">
         <v>12.15</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45733.55208333334</v>
+        <v>45734.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1115.9</v>
+        <v>1132.45</v>
       </c>
       <c r="I39" t="n">
         <v>1121.673589925246</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.71</v>
+        <v>-2.2</v>
       </c>
       <c r="L39" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
         <v>1.19</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.8</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45742.38541666666</v>
+        <v>45742.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1172.85</v>
+        <v>1156.2</v>
       </c>
       <c r="I40" t="n">
         <v>1156.331078089461</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>3.57</v>
+        <v>2.1</v>
       </c>
       <c r="L40" t="n">
         <v>1.4</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.64</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1170.6</v>
+        <v>1190.7</v>
       </c>
       <c r="I41" t="n">
         <v>1175.981890412592</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>22</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.25</v>
+        <v>-2.98</v>
       </c>
       <c r="L41" t="n">
         <v>9.609999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.84</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45784.55208333334</v>
+        <v>45785.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1199.4</v>
+        <v>1172.5</v>
       </c>
       <c r="I42" t="n">
         <v>1176.436558401636</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>0.73</v>
+        <v>-1.53</v>
       </c>
       <c r="L42" t="n">
         <v>1.99</v>
@@ -2835,7 +3338,7 @@
         <v>1.62</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="O42" t="n">
         <v>2.51</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1205</v>
+        <v>1231.5</v>
       </c>
       <c r="I43" t="n">
         <v>1229.71427142166</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.77</v>
+        <v>-5.03</v>
       </c>
       <c r="L43" t="n">
-        <v>3.18</v>
+        <v>6.73</v>
       </c>
       <c r="M43" t="n">
-        <v>0.08</v>
+        <v>1.66</v>
       </c>
       <c r="N43" t="n">
         <v>3.9</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1149.9</v>
+        <v>1141.5</v>
       </c>
       <c r="I44" t="n">
         <v>1142.166476590092</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.63</v>
+        <v>-7.31</v>
       </c>
       <c r="L44" t="n">
-        <v>7.18</v>
+        <v>8.15</v>
       </c>
       <c r="M44" t="n">
         <v>0.75</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1131</v>
+        <v>1162.4</v>
       </c>
       <c r="I45" t="n">
         <v>1138.408096557682</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>0.92</v>
+        <v>-1.83</v>
       </c>
       <c r="L45" t="n">
         <v>4.63</v>
@@ -3006,7 +3545,7 @@
         <v>2.22</v>
       </c>
       <c r="N45" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="O45" t="n">
         <v>-1.05</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.12</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1143</v>
+        <v>1130.6</v>
       </c>
       <c r="I46" t="n">
         <v>1134.397743211689</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.67</v>
+        <v>-2.74</v>
       </c>
       <c r="L46" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="M46" t="n">
         <v>1.12</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45866.55208333334</v>
+        <v>45867.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1124.9</v>
+        <v>1154.6</v>
       </c>
       <c r="I47" t="n">
         <v>1152.898084014364</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>-2.12</v>
       </c>
       <c r="L47" t="n">
         <v>3.2</v>
@@ -3120,7 +3683,7 @@
         <v>0.44</v>
       </c>
       <c r="N47" t="n">
-        <v>1.44</v>
+        <v>2.89</v>
       </c>
       <c r="O47" t="n">
         <v>-1.14</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.63</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1137.8</v>
+        <v>1089.9</v>
       </c>
       <c r="I48" t="n">
         <v>1111.773761648933</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.46</v>
+        <v>-5.6</v>
       </c>
       <c r="L48" t="n">
-        <v>2.83</v>
+        <v>6.02</v>
       </c>
       <c r="M48" t="n">
         <v>0.42</v>
       </c>
       <c r="N48" t="n">
-        <v>1.47</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
         <v>2.89</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.44</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1050.1</v>
+        <v>1097.3</v>
       </c>
       <c r="I49" t="n">
         <v>1063.672173896017</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>3.65</v>
+        <v>-0.68</v>
       </c>
       <c r="L49" t="n">
         <v>4.96</v>
@@ -3234,7 +3821,7 @@
         <v>1.84</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>5.77</v>
       </c>
       <c r="O49" t="n">
         <v>-5</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45938.38541666666</v>
+        <v>45938.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1080.8</v>
+        <v>1068.5</v>
       </c>
       <c r="I50" t="n">
         <v>1078.412474376667</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.5</v>
+        <v>-2.62</v>
       </c>
       <c r="L50" t="n">
         <v>3.28</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.01</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45939.55208333334</v>
+        <v>45940.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1118.9</v>
+        <v>1138.5</v>
       </c>
       <c r="I51" t="n">
         <v>1121.991127485856</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.72</v>
+        <v>-6.55</v>
       </c>
       <c r="L51" t="n">
-        <v>5.41</v>
+        <v>7.05</v>
       </c>
       <c r="M51" t="n">
         <v>2.67</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.13</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1187</v>
+        <v>1179.5</v>
       </c>
       <c r="I52" t="n">
         <v>1183.947230227146</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="L52" t="n">
         <v>5.13</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1210.5</v>
+        <v>1216.4</v>
       </c>
       <c r="I53" t="n">
         <v>1213.357157400259</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.63</v>
+        <v>-3.13</v>
       </c>
       <c r="L53" t="n">
-        <v>2.9</v>
+        <v>5.19</v>
       </c>
       <c r="M53" t="n">
         <v>0.41</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>3.57</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1195</v>
+        <v>1177.4</v>
       </c>
       <c r="I54" t="n">
         <v>1189.733170163441</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.76</v>
+        <v>-3.21</v>
       </c>
       <c r="L54" t="n">
         <v>3.8</v>
@@ -3519,7 +4166,7 @@
         <v>0.33</v>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.64</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1150</v>
+        <v>1187.9</v>
       </c>
       <c r="I55" t="n">
         <v>1182.955178688325</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>2.33</v>
+        <v>-0.89</v>
       </c>
       <c r="L55" t="n">
-        <v>1.73</v>
+        <v>3.17</v>
       </c>
       <c r="M55" t="n">
-        <v>1.29</v>
+        <v>3.48</v>
       </c>
       <c r="N55" t="n">
-        <v>1.6</v>
+        <v>4.25</v>
       </c>
       <c r="O55" t="n">
         <v>-2.1</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46063.38541666666</v>
+        <v>46063.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1146.8</v>
+        <v>1130.9</v>
       </c>
       <c r="I56" t="n">
         <v>1140.997067760527</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.46</v>
+        <v>-4.8</v>
       </c>
       <c r="L56" t="n">
-        <v>3.78</v>
+        <v>6.89</v>
       </c>
       <c r="M56" t="n">
         <v>0.33</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1221.7</v>
+        <v>1232.8</v>
       </c>
       <c r="I57" t="n">
         <v>1226.79461963707</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.029999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="L57" t="n">
         <v>10.61</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.79</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1549.5</v>
+        <v>1451.5</v>
       </c>
       <c r="I58" t="n">
         <v>1481.464089808593</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K58" t="n">
-        <v>25.69</v>
+        <v>17.74</v>
       </c>
       <c r="L58" t="n">
         <v>4.3</v>
@@ -3747,7 +4442,7 @@
         <v>2.77</v>
       </c>
       <c r="N58" t="n">
-        <v>2.04</v>
+        <v>5.26</v>
       </c>
       <c r="O58" t="n">
         <v>-0.14</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.35</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46191.55208333334</v>
+        <v>46192.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1444.7</v>
+        <v>1475.8</v>
       </c>
       <c r="I59" t="n">
         <v>1465.269490855444</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>0.47</v>
+        <v>-1.67</v>
       </c>
       <c r="L59" t="n">
         <v>4.72</v>
@@ -3804,7 +4511,7 @@
         <v>1.26</v>
       </c>
       <c r="N59" t="n">
-        <v>2.13</v>
+        <v>3.79</v>
       </c>
       <c r="O59" t="n">
         <v>-5.26</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.54</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46219.55208333334</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1550</v>
+        <v>1534</v>
       </c>
       <c r="I60" t="n">
         <v>1539.786527097426</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>5.03</v>
+        <v>3.94</v>
       </c>
       <c r="L60" t="n">
         <v>1.99</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.5</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1557</v>
+        <v>1594.9</v>
       </c>
       <c r="I61" t="n">
         <v>1591.195449188119</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.5</v>
+        <v>-3.97</v>
       </c>
       <c r="L61" t="n">
-        <v>3.31</v>
+        <v>4.22</v>
       </c>
       <c r="M61" t="n">
         <v>0.55</v>
       </c>
       <c r="N61" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="O61" t="n">
         <v>-0.9</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.88</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1682</v>
+        <v>1646.9</v>
       </c>
       <c r="I62" t="n">
         <v>1655.283505982875</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>70.16666666666667</v>
+        <v>71</v>
       </c>
       <c r="K62" t="n">
-        <v>5.46</v>
+        <v>3.26</v>
       </c>
       <c r="L62" t="n">
         <v>3.64</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,12 @@
       <c r="Q63" t="n">
         <v>26</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6898,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.4</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6908,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6918,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124.2</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6928,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6938,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6948,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70.2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -6197,7 +6958,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6207,7 +6968,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -6217,7 +6978,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75.40000000000001</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="14">
@@ -6227,7 +6988,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.96</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +6998,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.74</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.12</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7018,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.93</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7028,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.2</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7038,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.2</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7048,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.63</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="21">
@@ -6307,7 +7068,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7078,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7088,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="25">
@@ -6347,7 +7108,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +7118,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.32</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="28">
@@ -6367,7 +7128,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
